--- a/SE MILESTONE 1.xlsx
+++ b/SE MILESTONE 1.xlsx
@@ -526,9 +526,6 @@
     <t>amr.obaia@student.giu-berlin.de</t>
   </si>
   <si>
-    <t>youssef.tamer@student.giu-berlin.de</t>
-  </si>
-  <si>
     <t>ziad.farahat@student.giu-berlin.de</t>
   </si>
   <si>
@@ -536,6 +533,9 @@
   </si>
   <si>
     <t>kareem.elhamamhmy@student.giu-berlin.de</t>
+  </si>
+  <si>
+    <t>youssef.hassanismial@student.giu-berlin.de</t>
   </si>
 </sst>
 </file>
@@ -1406,7 +1406,7 @@
         <v>22001270</v>
       </c>
       <c r="C9" s="93" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D9" s="3">
         <v>1</v>
@@ -1414,13 +1414,13 @@
     </row>
     <row r="10" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="91" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B10" s="56">
         <v>22001257</v>
       </c>
       <c r="C10" s="93" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D10" s="56">
         <v>2</v>
@@ -1434,7 +1434,7 @@
         <v>22001513</v>
       </c>
       <c r="C11" s="93" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D11" s="59">
         <v>2</v>
